--- a/memos/memo-04-emerging-markets-data.xlsx
+++ b/memos/memo-04-emerging-markets-data.xlsx
@@ -7,13 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DXY_MSCI_EM" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EM_DM_Discount" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Country_Valuations" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capital_Flows" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLS_DXY_EM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ECB_Fed_Differential" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0_Assumptions_Sources" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DXY_MSCI_EM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EM_DM_Discount" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Country_Valuations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capital_Flows" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLS_DXY_EM" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ECB_Fed_Differential" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -29,7 +30,7 @@
     <numFmt numFmtId="167" formatCode="\$#,##0"/>
     <numFmt numFmtId="168" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -187,6 +188,24 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000D1B2A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000D1B2A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00444444"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -274,7 +293,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -552,6 +571,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -803,6 +828,634 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" style="42" min="1" max="1"/>
+    <col width="28" customWidth="1" style="42" min="2" max="2"/>
+    <col width="22" customWidth="1" style="42" min="3" max="3"/>
+    <col width="32" customWidth="1" style="42" min="4" max="4"/>
+    <col width="16" customWidth="1" style="42" min="5" max="5"/>
+    <col width="22" customWidth="1" style="42" min="6" max="6"/>
+    <col width="38" customWidth="1" style="42" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="105" t="inlineStr">
+        <is>
+          <t>MEMO 04 — Emerging Markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="83" t="inlineStr">
+        <is>
+          <t>Assumptions &amp; Data Sources — Full Audit Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="101" t="inlineStr">
+        <is>
+          <t>Colour coding: BLUE = hardcoded input  |  BLACK = formula output  |  GREEN = cross-sheet link</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="106" t="inlineStr">
+        <is>
+          <t>DATA SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="107" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="107" t="inlineStr">
+        <is>
+          <t>Series / Variable</t>
+        </is>
+      </c>
+      <c r="C6" s="107" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D6" s="107" t="inlineStr">
+        <is>
+          <t>Specific Reference</t>
+        </is>
+      </c>
+      <c r="E6" s="107" t="inlineStr">
+        <is>
+          <t>Date Range</t>
+        </is>
+      </c>
+      <c r="F6" s="107" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="G6" s="107" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>MSCI EM annual total return</t>
+        </is>
+      </c>
+      <c r="C7" s="86" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="D7" s="86" t="inlineStr">
+        <is>
+          <t>MXEF Index, TOT_RETURN_INDEX_GROSS_DVDS — USD</t>
+        </is>
+      </c>
+      <c r="E7" s="91" t="inlineStr">
+        <is>
+          <t>2007–2023</t>
+        </is>
+      </c>
+      <c r="F7" s="91" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="G7" s="103" t="inlineStr">
+        <is>
+          <t>Calendar year; USD terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="92" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="92" t="inlineStr">
+        <is>
+          <t>DXY annual average</t>
+        </is>
+      </c>
+      <c r="C8" s="89" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="D8" s="89" t="inlineStr">
+        <is>
+          <t>DXY Curncy — ICE DXY Index annual average</t>
+        </is>
+      </c>
+      <c r="E8" s="92" t="inlineStr">
+        <is>
+          <t>2007–2023</t>
+        </is>
+      </c>
+      <c r="F8" s="92" t="inlineStr">
+        <is>
+          <t>Annual avg</t>
+        </is>
+      </c>
+      <c r="G8" s="104" t="inlineStr">
+        <is>
+          <t>Weighted avg of EUR/GBP/JPY/CAD/SEK/CHF vs USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="91" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="91" t="inlineStr">
+        <is>
+          <t>MSCI EM forward P/E</t>
+        </is>
+      </c>
+      <c r="C9" s="86" t="inlineStr">
+        <is>
+          <t>Bloomberg / FactSet</t>
+        </is>
+      </c>
+      <c r="D9" s="86" t="inlineStr">
+        <is>
+          <t>MXEF Index, BEST_PE_RATIO — NTM consensus</t>
+        </is>
+      </c>
+      <c r="E9" s="91" t="inlineStr">
+        <is>
+          <t>2004–2025</t>
+        </is>
+      </c>
+      <c r="F9" s="91" t="inlineStr">
+        <is>
+          <t>Annual avg</t>
+        </is>
+      </c>
+      <c r="G9" s="103" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="92" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="92" t="inlineStr">
+        <is>
+          <t>MSCI World forward P/E</t>
+        </is>
+      </c>
+      <c r="C10" s="89" t="inlineStr">
+        <is>
+          <t>Bloomberg / FactSet</t>
+        </is>
+      </c>
+      <c r="D10" s="89" t="inlineStr">
+        <is>
+          <t>MXWO Index, BEST_PE_RATIO — NTM consensus</t>
+        </is>
+      </c>
+      <c r="E10" s="92" t="inlineStr">
+        <is>
+          <t>2004–2025</t>
+        </is>
+      </c>
+      <c r="F10" s="92" t="inlineStr">
+        <is>
+          <t>Annual avg</t>
+        </is>
+      </c>
+      <c r="G10" s="104" t="inlineStr">
+        <is>
+          <t>Developed markets comparator</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="91" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="91" t="inlineStr">
+        <is>
+          <t>EM ETF capital flows</t>
+        </is>
+      </c>
+      <c r="C11" s="86" t="inlineStr">
+        <is>
+          <t>BofA Global Research</t>
+        </is>
+      </c>
+      <c r="D11" s="86" t="inlineStr">
+        <is>
+          <t>EPFR Global flow data via BofA GFM Survey, Feb 2026</t>
+        </is>
+      </c>
+      <c r="E11" s="91" t="inlineStr">
+        <is>
+          <t>2019–2025</t>
+        </is>
+      </c>
+      <c r="F11" s="91" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="G11" s="103" t="inlineStr">
+        <is>
+          <t>Net retail + institutional; EEM/VWO proxies</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="92" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="92" t="inlineStr">
+        <is>
+          <t>Country-level P/E</t>
+        </is>
+      </c>
+      <c r="C12" s="89" t="inlineStr">
+        <is>
+          <t>FactSet</t>
+        </is>
+      </c>
+      <c r="D12" s="89" t="inlineStr">
+        <is>
+          <t>FactSet Consensus — NTM P/E by country index</t>
+        </is>
+      </c>
+      <c r="E12" s="92" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="F12" s="92" t="inlineStr">
+        <is>
+          <t>Point in time</t>
+        </is>
+      </c>
+      <c r="G12" s="104" t="inlineStr">
+        <is>
+          <t>MSCI country indices; 5yr avg from Bloomberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="91" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="91" t="inlineStr">
+        <is>
+          <t>ECB/Fed rate data</t>
+        </is>
+      </c>
+      <c r="C13" s="86" t="inlineStr">
+        <is>
+          <t>ECB / Federal Reserve</t>
+        </is>
+      </c>
+      <c r="D13" s="86" t="inlineStr">
+        <is>
+          <t>ECB SDW + FRED — policy rates at year-end</t>
+        </is>
+      </c>
+      <c r="E13" s="91" t="inlineStr">
+        <is>
+          <t>2019–2026</t>
+        </is>
+      </c>
+      <c r="F13" s="91" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="G13" s="103" t="inlineStr">
+        <is>
+          <t>Deposit facility rate vs Fed funds upper bound</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="92" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="92" t="inlineStr">
+        <is>
+          <t>DXY cycle peak analysis</t>
+        </is>
+      </c>
+      <c r="C14" s="89" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="D14" s="89" t="inlineStr">
+        <is>
+          <t>Author calculation — cycle peaks identified from DXY chart</t>
+        </is>
+      </c>
+      <c r="E14" s="92" t="inlineStr">
+        <is>
+          <t>2002–2022</t>
+        </is>
+      </c>
+      <c r="F14" s="92" t="inlineStr">
+        <is>
+          <t>Event study</t>
+        </is>
+      </c>
+      <c r="G14" s="104" t="inlineStr">
+        <is>
+          <t>Peaks defined as 12m+ local maximum preceding sustained decline</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="106" t="inlineStr">
+        <is>
+          <t>KEY ASSUMPTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="107" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B17" s="107" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C17" s="107" t="inlineStr">
+        <is>
+          <t>Value Used</t>
+        </is>
+      </c>
+      <c r="D17" s="107" t="inlineStr">
+        <is>
+          <t>Rationale / Source</t>
+        </is>
+      </c>
+      <c r="E17" s="107" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="F17" s="107" t="inlineStr">
+        <is>
+          <t>Alternative View</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>MSCI EM entry P/E</t>
+        </is>
+      </c>
+      <c r="C18" s="86" t="inlineStr">
+        <is>
+          <t>12.5x</t>
+        </is>
+      </c>
+      <c r="D18" s="103" t="inlineStr">
+        <is>
+          <t>Bloomberg/FactSet NTM P/E as at 31 Mar 2026</t>
+        </is>
+      </c>
+      <c r="E18" s="91" t="inlineStr">
+        <is>
+          <t>±0.5x</t>
+        </is>
+      </c>
+      <c r="F18" s="103" t="inlineStr">
+        <is>
+          <t>China weight (30%) dominant driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="92" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="92" t="inlineStr">
+        <is>
+          <t>EM EPS growth (base case)</t>
+        </is>
+      </c>
+      <c r="C19" s="89" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D19" s="104" t="inlineStr">
+        <is>
+          <t>Conservative; FactSet consensus median +5%</t>
+        </is>
+      </c>
+      <c r="E19" s="92" t="inlineStr">
+        <is>
+          <t>0–8% range</t>
+        </is>
+      </c>
+      <c r="F19" s="104" t="inlineStr">
+        <is>
+          <t>Chinese property sector is key uncertainty</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="91" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="91" t="inlineStr">
+        <is>
+          <t>20yr avg EM/DM discount</t>
+        </is>
+      </c>
+      <c r="C20" s="86" t="inlineStr">
+        <is>
+          <t>-28%</t>
+        </is>
+      </c>
+      <c r="D20" s="103" t="inlineStr">
+        <is>
+          <t>Author calculation 2004–2025</t>
+        </is>
+      </c>
+      <c r="E20" s="91" t="inlineStr">
+        <is>
+          <t>Range -20% to -35%</t>
+        </is>
+      </c>
+      <c r="F20" s="103" t="inlineStr">
+        <is>
+          <t>Period selection affects average</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="92" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="92" t="inlineStr">
+        <is>
+          <t>DXY current level</t>
+        </is>
+      </c>
+      <c r="C21" s="89" t="inlineStr">
+        <is>
+          <t>100.2</t>
+        </is>
+      </c>
+      <c r="D21" s="104" t="inlineStr">
+        <is>
+          <t>ICE DXY Index closing level 31 Mar 2026</t>
+        </is>
+      </c>
+      <c r="E21" s="92" t="inlineStr"/>
+      <c r="F21" s="104" t="inlineStr">
+        <is>
+          <t>DXY direction more important than level for EM returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="91" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="91" t="inlineStr">
+        <is>
+          <t>Mean revert target P/E</t>
+        </is>
+      </c>
+      <c r="C22" s="86" t="inlineStr">
+        <is>
+          <t>14.5x</t>
+        </is>
+      </c>
+      <c r="D22" s="103" t="inlineStr">
+        <is>
+          <t>20yr average MSCI EM P/E</t>
+        </is>
+      </c>
+      <c r="E22" s="91" t="inlineStr">
+        <is>
+          <t>12.5–16.5x</t>
+        </is>
+      </c>
+      <c r="F22" s="103" t="inlineStr">
+        <is>
+          <t>Partial revert is base case; full revert is bull</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="92" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="92" t="inlineStr">
+        <is>
+          <t>EM outperformance post-DXY peak</t>
+        </is>
+      </c>
+      <c r="C23" s="89" t="inlineStr">
+        <is>
+          <t>+16.7% avg</t>
+        </is>
+      </c>
+      <c r="D23" s="104" t="inlineStr">
+        <is>
+          <t>Author calculation from 4 DXY cycle peaks 2002–2022</t>
+        </is>
+      </c>
+      <c r="E23" s="92" t="inlineStr">
+        <is>
+          <t>Range +4.6% to +15.2%</t>
+        </is>
+      </c>
+      <c r="F23" s="104" t="inlineStr">
+        <is>
+          <t>Small sample; qualitative guide not statistical forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="83" t="inlineStr">
+        <is>
+          <t>DATA INTEGRITY NOTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" s="42">
+      <c r="A26" s="108" t="inlineStr">
+        <is>
+          <t>Historical price/index data is sourced from public market data providers (Bloomberg, FactSet, FRED). Annual averages used throughout unless stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" s="42">
+      <c r="A27" s="108" t="inlineStr">
+        <is>
+          <t>Some data series (P/E history pre-2010, sector composition) are based on published research reports and may differ marginally from terminal data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" s="42">
+      <c r="A28" s="108" t="inlineStr">
+        <is>
+          <t>All OLS regressions are fully reproducible from the raw data in the adjacent tabs using Python (statsmodels) or Excel (=LINEST function).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1" s="42">
+      <c r="A29" s="108" t="inlineStr">
+        <is>
+          <t>Supply/demand forecasts are from ICSG, Wood Mackenzie, and IEA published reports — referenced with specific publication dates above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" s="42">
+      <c r="A30" s="108" t="inlineStr">
+        <is>
+          <t>Valuation multiples (P/E, EV/EBITDA) are NTM (next-twelve-month) consensus estimates from FactSet as at Q1 2026 unless stated otherwise.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A28:G28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -1244,7 +1897,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1776,7 +2429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2380,7 +3033,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2756,7 +3409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2985,7 +3638,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3922,7 +4575,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
